--- a/filter_usage.xlsx
+++ b/filter_usage.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,46 @@
           <t>이슈메모</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1785130829264</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>05:40</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H2" t="n">
+        <v>120</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
